--- a/artfynd/A 23127-2026 artfynd.xlsx
+++ b/artfynd/A 23127-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>68154017</v>
+        <v>68154019</v>
       </c>
       <c r="B2" t="n">
-        <v>90655</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>788</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590198.8925797782</v>
+        <v>590185</v>
       </c>
       <c r="R2" t="n">
-        <v>6468826.16780816</v>
+        <v>6468872</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2017-10-26</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2017-10-26</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>68154016</v>
+        <v>68154017</v>
       </c>
       <c r="B3" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93199</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>788</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590205.8049947779</v>
+        <v>590199</v>
       </c>
       <c r="R3" t="n">
-        <v>6468776.976125952</v>
+        <v>6468826</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -860,19 +840,9 @@
           <t>2017-10-26</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2017-10-26</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>68154020</v>
+        <v>68154016</v>
       </c>
       <c r="B4" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590158.9642997205</v>
+        <v>590206</v>
       </c>
       <c r="R4" t="n">
-        <v>6468916.07688171</v>
+        <v>6468777</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -972,19 +937,9 @@
           <t>2017-10-26</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2017-10-26</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,12 +969,7 @@
         <v>68154018</v>
       </c>
       <c r="B5" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1051,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590186.7955308945</v>
+        <v>590187</v>
       </c>
       <c r="R5" t="n">
-        <v>6468872.090203315</v>
+        <v>6468872</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1084,19 +1034,9 @@
           <t>2017-10-26</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2017-10-26</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>68154019</v>
+        <v>68154023</v>
       </c>
       <c r="B6" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590185.2184638248</v>
+        <v>590061</v>
       </c>
       <c r="R6" t="n">
-        <v>6468872.054087433</v>
+        <v>6468961</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1196,19 +1131,9 @@
           <t>2017-10-26</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2017-10-26</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,37 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>68154022</v>
+        <v>68153978</v>
       </c>
       <c r="B7" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221144</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590093.8320968794</v>
+        <v>590032</v>
       </c>
       <c r="R7" t="n">
-        <v>6468981.258717085</v>
+        <v>6468754</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1308,19 +1228,9 @@
           <t>2017-10-26</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2017-10-26</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1344,6 +1254,200 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>68154020</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Hösterum, Fredrikslund, Ög</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>590159</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6468916</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Mogata</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2017-10-26</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2017-10-26</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>68154022</v>
+      </c>
+      <c r="B9" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Hösterum, Fredrikslund, Ög</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>590094</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6468981</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Mogata</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2017-10-26</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2017-10-26</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23127-2026 artfynd.xlsx
+++ b/artfynd/A 23127-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -772,48 +772,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>68154017</v>
+        <v>134636770</v>
       </c>
       <c r="B3" t="n">
-        <v>93199</v>
+        <v>79039</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>788</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hösterum, Fredrikslund, Ög</t>
+          <t>Fredrikslund, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590199</v>
+        <v>590148</v>
       </c>
       <c r="R3" t="n">
-        <v>6468826</v>
+        <v>6468845</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -837,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2017-10-26</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2017-10-26</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -857,22 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>68154016</v>
+        <v>134636771</v>
       </c>
       <c r="B4" t="n">
-        <v>93235</v>
+        <v>79039</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,37 +880,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hösterum, Fredrikslund, Ög</t>
+          <t>Fredrikslund, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590206</v>
+        <v>590177</v>
       </c>
       <c r="R4" t="n">
-        <v>6468777</v>
+        <v>6468871</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -934,12 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2017-10-26</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2017-10-26</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -954,22 +954,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>68154018</v>
+        <v>134636772</v>
       </c>
       <c r="B5" t="n">
-        <v>93235</v>
+        <v>79039</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,37 +977,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hösterum, Fredrikslund, Ög</t>
+          <t>Fredrikslund, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590187</v>
+        <v>590175</v>
       </c>
       <c r="R5" t="n">
-        <v>6468872</v>
+        <v>6468870</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2017-10-26</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2017-10-26</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1051,22 +1051,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>68154023</v>
+        <v>134636773</v>
       </c>
       <c r="B6" t="n">
-        <v>93235</v>
+        <v>79039</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,37 +1074,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hösterum, Fredrikslund, Ög</t>
+          <t>Fredrikslund, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590061</v>
+        <v>590174</v>
       </c>
       <c r="R6" t="n">
-        <v>6468961</v>
+        <v>6468870</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1128,12 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2017-10-26</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2017-10-26</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1148,22 +1148,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>68153978</v>
+        <v>134636783</v>
       </c>
       <c r="B7" t="n">
-        <v>79946</v>
+        <v>79039</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,37 +1171,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hösterum, Fredrikslund, Ög</t>
+          <t>Fredrikslund, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590032</v>
+        <v>590119</v>
       </c>
       <c r="R7" t="n">
-        <v>6468754</v>
+        <v>6468844</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1225,12 +1225,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2017-10-26</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2017-10-26</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1245,44 +1245,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>68154020</v>
+        <v>68154017</v>
       </c>
       <c r="B8" t="n">
-        <v>79946</v>
+        <v>93199</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>788</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590159</v>
+        <v>590199</v>
       </c>
       <c r="R8" t="n">
-        <v>6468916</v>
+        <v>6468826</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>68154022</v>
+        <v>134636769</v>
       </c>
       <c r="B9" t="n">
-        <v>106244</v>
+        <v>96783</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,37 +1365,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221144</v>
+        <v>2180</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hösterum, Fredrikslund, Ög</t>
+          <t>Fredrikslund, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590094</v>
+        <v>590157</v>
       </c>
       <c r="R9" t="n">
-        <v>6468981</v>
+        <v>6468813</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2017-10-26</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2017-10-26</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1439,15 +1439,2172 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>134636774</v>
+      </c>
+      <c r="B10" t="n">
+        <v>96783</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Fredrikslund, Ög</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>590152</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6468906</v>
+      </c>
+      <c r="S10" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Mogata</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>134636778</v>
+      </c>
+      <c r="B11" t="n">
+        <v>96783</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Fredrikslund, Ög</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>590133</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6468922</v>
+      </c>
+      <c r="S11" t="n">
+        <v>15</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Mogata</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>134636779</v>
+      </c>
+      <c r="B12" t="n">
+        <v>96783</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Fredrikslund, Ög</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>590109</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6468908</v>
+      </c>
+      <c r="S12" t="n">
+        <v>15</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Mogata</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>134636781</v>
+      </c>
+      <c r="B13" t="n">
+        <v>96783</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Fredrikslund, Ög</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>590129</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6468895</v>
+      </c>
+      <c r="S13" t="n">
+        <v>15</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Mogata</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>134636762</v>
+      </c>
+      <c r="B14" t="n">
+        <v>93271</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Fredrikslund, Ög</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>590106</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6468839</v>
+      </c>
+      <c r="S14" t="n">
+        <v>15</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Mogata</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>134636767</v>
+      </c>
+      <c r="B15" t="n">
+        <v>93271</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Fredrikslund, Ög</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>590157</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6468813</v>
+      </c>
+      <c r="S15" t="n">
+        <v>15</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Mogata</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>134636371</v>
+      </c>
+      <c r="B16" t="n">
+        <v>92385</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>5420</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Grovticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Phaeolus schweinitzii</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Fredrikslund, Ög</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>590105</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6468783</v>
+      </c>
+      <c r="S16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Mogata</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>68154016</v>
+      </c>
+      <c r="B17" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Hösterum, Fredrikslund, Ög</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>590206</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6468777</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Mogata</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2017-10-26</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2017-10-26</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
           <t>Mikael Hagström</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
+      <c r="AX17" t="inlineStr">
         <is>
           <t>Mikael Hagström</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr"/>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>68154018</v>
+      </c>
+      <c r="B18" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Hösterum, Fredrikslund, Ög</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>590187</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6468872</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Mogata</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2017-10-26</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2017-10-26</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>68154023</v>
+      </c>
+      <c r="B19" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Hösterum, Fredrikslund, Ög</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>590061</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6468961</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Mogata</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2017-10-26</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2017-10-26</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>68153978</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Hösterum, Fredrikslund, Ög</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>590032</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6468754</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Mogata</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2017-10-26</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2017-10-26</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>68154020</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Hösterum, Fredrikslund, Ög</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>590159</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6468916</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Mogata</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2017-10-26</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2017-10-26</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>134636370</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Fredrikslund, Ög</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>590126</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6468749</v>
+      </c>
+      <c r="S22" t="n">
+        <v>15</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Mogata</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>134636763</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Fredrikslund, Ög</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>590148</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6468821</v>
+      </c>
+      <c r="S23" t="n">
+        <v>15</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Mogata</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>134636782</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Fredrikslund, Ög</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>590107</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6468848</v>
+      </c>
+      <c r="S24" t="n">
+        <v>15</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Mogata</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>134636765</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Fredrikslund, Ög</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>590148</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6468813</v>
+      </c>
+      <c r="S25" t="n">
+        <v>15</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Mogata</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>134636784</v>
+      </c>
+      <c r="B26" t="n">
+        <v>5181</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Fredrikslund, Ög</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>590091</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6468824</v>
+      </c>
+      <c r="S26" t="n">
+        <v>15</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Mogata</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>134636760</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Fredrikslund, Ög</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>590099</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6468802</v>
+      </c>
+      <c r="S27" t="n">
+        <v>15</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Mogata</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>134636761</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Fredrikslund, Ög</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>590108</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6468828</v>
+      </c>
+      <c r="S28" t="n">
+        <v>15</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Mogata</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>134636764</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Fredrikslund, Ög</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>590164</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6468809</v>
+      </c>
+      <c r="S29" t="n">
+        <v>15</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Mogata</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>68154022</v>
+      </c>
+      <c r="B30" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Hösterum, Fredrikslund, Ög</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>590094</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6468981</v>
+      </c>
+      <c r="S30" t="n">
+        <v>25</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Mogata</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2017-10-26</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2017-10-26</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>134636766</v>
+      </c>
+      <c r="B31" t="n">
+        <v>106324</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Fredrikslund, Ög</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>590156</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6468813</v>
+      </c>
+      <c r="S31" t="n">
+        <v>15</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Mogata</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23127-2026 artfynd.xlsx
+++ b/artfynd/A 23127-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AZ31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68154019</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134636770</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134636771</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134636772</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134636773</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134636783</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68154017</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134636769</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134636774</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134636778</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134636779</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134636781</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134636762</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134636767</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134636371</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68154016</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68154018</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,6 +2508,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68154023</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2515,6 +2610,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68153978</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2612,6 +2712,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68154020</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2709,6 +2814,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134636370</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2806,6 +2916,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134636763</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2903,6 +3018,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134636782</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3008,6 +3128,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134636765</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3105,6 +3230,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134636784</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3207,6 +3337,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134636760</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3309,6 +3444,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134636761</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3411,6 +3551,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134636764</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3508,6 +3653,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68154022</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3605,8 +3755,45 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134636766</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>